--- a/tugas-1.xlsx
+++ b/tugas-1.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Belajar Excell\belajar-excell\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53318BE2-1A5C-490E-BBFA-F7378F038890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA9DAE0F-D390-4179-B172-E83AB757A02E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{DCFC0827-0EF9-42A2-9AA5-829752BCFC3E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{DCFC0827-0EF9-42A2-9AA5-829752BCFC3E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="soal" sheetId="3" r:id="rId2"/>
+    <sheet name="data referensi" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="60">
   <si>
     <t xml:space="preserve">Nama Murid </t>
   </si>
@@ -121,6 +123,99 @@
   </si>
   <si>
     <t>Rata rata nilai murid yang Lulus</t>
+  </si>
+  <si>
+    <t>SOAL ADMIN LOGISTIK</t>
+  </si>
+  <si>
+    <t>Tanggal Pemesanan</t>
+  </si>
+  <si>
+    <t>No. Pemesanan</t>
+  </si>
+  <si>
+    <t>Nama Customer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Domisili </t>
+  </si>
+  <si>
+    <t>Lama Pengiriman (Hari)</t>
+  </si>
+  <si>
+    <t>Tanggal Sampai</t>
+  </si>
+  <si>
+    <t>SOAL LATIHAN LOGISTIK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nama Customer </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jenis Kelamin </t>
+  </si>
+  <si>
+    <t>Domisili</t>
+  </si>
+  <si>
+    <t>Alvin</t>
+  </si>
+  <si>
+    <t>Hardi</t>
+  </si>
+  <si>
+    <t>Laura</t>
+  </si>
+  <si>
+    <t>Putri</t>
+  </si>
+  <si>
+    <t>Ahmad</t>
+  </si>
+  <si>
+    <t>Fadlan</t>
+  </si>
+  <si>
+    <t>Gita</t>
+  </si>
+  <si>
+    <t>Jaka</t>
+  </si>
+  <si>
+    <t>Salsa</t>
+  </si>
+  <si>
+    <t>Novi</t>
+  </si>
+  <si>
+    <t>Laki-laki</t>
+  </si>
+  <si>
+    <t>Perempuan</t>
+  </si>
+  <si>
+    <t>Surabaya</t>
+  </si>
+  <si>
+    <t>Bandung</t>
+  </si>
+  <si>
+    <t>Medan</t>
+  </si>
+  <si>
+    <t>Jakarta</t>
+  </si>
+  <si>
+    <t>Palembang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kota </t>
+  </si>
+  <si>
+    <t>Lama Pengiriman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palembang </t>
   </si>
 </sst>
 </file>
@@ -129,10 +224,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="0.0"/>
-    <numFmt numFmtId="172" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -157,16 +252,51 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="7" tint="0.39997558519241921"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="7" tint="0.39997558519241921"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="7" tint="0.39997558519241921"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -241,12 +371,74 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -260,14 +452,44 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -993,4 +1215,521 @@
     <brk id="5" max="10" man="1"/>
   </colBreaks>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00BEA6B0-A8D1-4344-A5C9-A9CC1CDAD27B}">
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="4" width="15.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="17"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="18"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="20"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="14">
+        <v>290</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="14">
+        <v>291</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="14">
+        <v>292</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="14">
+        <v>293</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="14">
+        <v>294</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="14">
+        <v>295</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="14">
+        <v>296</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="14">
+        <v>297</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="14">
+        <v>298</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="14">
+        <v>299</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+    </row>
+    <row r="15" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="16" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17" s="4">
+        <v>2</v>
+      </c>
+      <c r="C17" s="4">
+        <v>1</v>
+      </c>
+      <c r="D17" s="4">
+        <v>4</v>
+      </c>
+      <c r="E17" s="4">
+        <v>3</v>
+      </c>
+      <c r="F17" s="4">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2857D02-9512-4E36-9283-16F2ADB36667}">
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="7" width="20.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A1" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="21">
+        <v>44261</v>
+      </c>
+      <c r="B3" s="3">
+        <v>295</v>
+      </c>
+      <c r="C3" s="3" t="str">
+        <f>VLOOKUP(B3,soal!$A$4:$D$13,2,0)</f>
+        <v>Fadlan</v>
+      </c>
+      <c r="D3" s="3" t="str">
+        <f>VLOOKUP(B3,soal!$A$4:$D$13,4,0)</f>
+        <v>Palembang</v>
+      </c>
+      <c r="E3" s="24" t="e">
+        <f>HLOOKUP(D3,soal!$B$16:$F$17,2,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F3" s="21" t="e">
+        <f>A3+E3</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="21">
+        <v>44262</v>
+      </c>
+      <c r="B4" s="3">
+        <v>298</v>
+      </c>
+      <c r="C4" s="3" t="str">
+        <f>VLOOKUP(B4,soal!$A$4:$D$13,2,0)</f>
+        <v>Salsa</v>
+      </c>
+      <c r="D4" s="3" t="str">
+        <f>VLOOKUP(B4,soal!$A$4:$D$13,4,0)</f>
+        <v>Jakarta</v>
+      </c>
+      <c r="E4" s="3">
+        <f>HLOOKUP(D4,soal!$B$16:$F$17,2,0)</f>
+        <v>2</v>
+      </c>
+      <c r="F4" s="21">
+        <f t="shared" ref="F4:F12" si="0">A4+E4</f>
+        <v>44264</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="21">
+        <v>44263</v>
+      </c>
+      <c r="B5" s="3">
+        <v>291</v>
+      </c>
+      <c r="C5" s="3" t="str">
+        <f>VLOOKUP(B5,soal!$A$4:$D$13,2,0)</f>
+        <v>Hardi</v>
+      </c>
+      <c r="D5" s="3" t="str">
+        <f>VLOOKUP(B5,soal!$A$4:$D$13,4,0)</f>
+        <v>Bandung</v>
+      </c>
+      <c r="E5" s="3">
+        <f>HLOOKUP(D5,soal!$B$16:$F$17,2,0)</f>
+        <v>1</v>
+      </c>
+      <c r="F5" s="21">
+        <f t="shared" si="0"/>
+        <v>44264</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="21">
+        <v>44264</v>
+      </c>
+      <c r="B6" s="3">
+        <v>299</v>
+      </c>
+      <c r="C6" s="3" t="str">
+        <f>VLOOKUP(B6,soal!$A$4:$D$13,2,0)</f>
+        <v>Novi</v>
+      </c>
+      <c r="D6" s="3" t="str">
+        <f>VLOOKUP(B6,soal!$A$4:$D$13,4,0)</f>
+        <v>Palembang</v>
+      </c>
+      <c r="E6" s="3" t="e">
+        <f>HLOOKUP(D6,soal!$B$16:$F$17,2,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F6" s="21" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="21">
+        <v>44265</v>
+      </c>
+      <c r="B7" s="3">
+        <v>292</v>
+      </c>
+      <c r="C7" s="3" t="str">
+        <f>VLOOKUP(B7,soal!$A$4:$D$13,2,0)</f>
+        <v>Laura</v>
+      </c>
+      <c r="D7" s="3" t="str">
+        <f>VLOOKUP(B7,soal!$A$4:$D$13,4,0)</f>
+        <v>Medan</v>
+      </c>
+      <c r="E7" s="3">
+        <f>HLOOKUP(D7,soal!$B$16:$F$17,2,0)</f>
+        <v>5</v>
+      </c>
+      <c r="F7" s="21">
+        <f t="shared" si="0"/>
+        <v>44270</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="21">
+        <v>44266</v>
+      </c>
+      <c r="B8" s="3">
+        <v>296</v>
+      </c>
+      <c r="C8" s="3" t="str">
+        <f>VLOOKUP(B8,soal!$A$4:$D$13,2,0)</f>
+        <v>Gita</v>
+      </c>
+      <c r="D8" s="3" t="str">
+        <f>VLOOKUP(B8,soal!$A$4:$D$13,4,0)</f>
+        <v>Surabaya</v>
+      </c>
+      <c r="E8" s="3">
+        <f>HLOOKUP(D8,soal!$B$16:$F$17,2,0)</f>
+        <v>3</v>
+      </c>
+      <c r="F8" s="21">
+        <f t="shared" si="0"/>
+        <v>44269</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="21">
+        <v>44267</v>
+      </c>
+      <c r="B9" s="3">
+        <v>293</v>
+      </c>
+      <c r="C9" s="3" t="str">
+        <f>VLOOKUP(B9,soal!$A$4:$D$13,2,0)</f>
+        <v>Putri</v>
+      </c>
+      <c r="D9" s="3" t="str">
+        <f>VLOOKUP(B9,soal!$A$4:$D$13,4,0)</f>
+        <v>Bandung</v>
+      </c>
+      <c r="E9" s="3">
+        <f>HLOOKUP(D9,soal!$B$16:$F$17,2,0)</f>
+        <v>1</v>
+      </c>
+      <c r="F9" s="21">
+        <f t="shared" si="0"/>
+        <v>44268</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="21">
+        <v>44268</v>
+      </c>
+      <c r="B10" s="3">
+        <v>290</v>
+      </c>
+      <c r="C10" s="3" t="str">
+        <f>VLOOKUP(B10,soal!$A$4:$D$13,2,0)</f>
+        <v>Alvin</v>
+      </c>
+      <c r="D10" s="3" t="str">
+        <f>VLOOKUP(B10,soal!$A$4:$D$13,4,0)</f>
+        <v>Surabaya</v>
+      </c>
+      <c r="E10" s="3">
+        <f>HLOOKUP(D10,soal!$B$16:$F$17,2,0)</f>
+        <v>3</v>
+      </c>
+      <c r="F10" s="21">
+        <f t="shared" si="0"/>
+        <v>44271</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="21">
+        <v>44269</v>
+      </c>
+      <c r="B11" s="3">
+        <v>294</v>
+      </c>
+      <c r="C11" s="3" t="str">
+        <f>VLOOKUP(B11,soal!$A$4:$D$13,2,0)</f>
+        <v>Ahmad</v>
+      </c>
+      <c r="D11" s="3" t="str">
+        <f>VLOOKUP(B11,soal!$A$4:$D$13,4,0)</f>
+        <v>Jakarta</v>
+      </c>
+      <c r="E11" s="3">
+        <f>HLOOKUP(D11,soal!$B$16:$F$17,2,0)</f>
+        <v>2</v>
+      </c>
+      <c r="F11" s="21">
+        <f t="shared" si="0"/>
+        <v>44271</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="21">
+        <v>44270</v>
+      </c>
+      <c r="B12" s="3">
+        <v>297</v>
+      </c>
+      <c r="C12" s="3" t="str">
+        <f>VLOOKUP(B12,soal!$A$4:$D$13,2,0)</f>
+        <v>Jaka</v>
+      </c>
+      <c r="D12" s="3" t="str">
+        <f>VLOOKUP(B12,soal!$A$4:$D$13,4,0)</f>
+        <v>Medan</v>
+      </c>
+      <c r="E12" s="3">
+        <f>HLOOKUP(D12,soal!$B$16:$F$17,2,0)</f>
+        <v>5</v>
+      </c>
+      <c r="F12" s="21">
+        <f t="shared" si="0"/>
+        <v>44275</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>